--- a/samples/tracking01/tracking02.xlsx
+++ b/samples/tracking01/tracking02.xlsx
@@ -1676,7 +1676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>frame_index</t>
+          <t>frame_index_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
